--- a/aReport_card/2025_2026/Second_term/JSS1/Second_term_JSS1_Civic_Education.xlsx
+++ b/aReport_card/2025_2026/Second_term/JSS1/Second_term_JSS1_Civic_Education.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B521401-A89F-4B5B-A64D-8AF109FFBE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22200323-76CA-449C-8006-DF9DB2F80A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -501,13 +501,14 @@
         <v>34</v>
       </c>
       <c r="D2" s="1">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E2" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>77</v>
+        <f>C2+D2+E2</f>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -521,13 +522,14 @@
         <v>33</v>
       </c>
       <c r="D3" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E3" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>76</v>
+        <f>C3+D3+E3</f>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -541,13 +543,14 @@
         <v>33</v>
       </c>
       <c r="D4" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>76</v>
+        <f>C4+D4+E4</f>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -558,16 +561,16 @@
         <v>13</v>
       </c>
       <c r="C5" s="1">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -581,13 +584,13 @@
         <v>33</v>
       </c>
       <c r="D6" s="1">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="E6" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -598,16 +601,16 @@
         <v>15</v>
       </c>
       <c r="C7" s="1">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D7" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -621,13 +624,13 @@
         <v>34</v>
       </c>
       <c r="D8" s="1">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E8" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -641,13 +644,13 @@
         <v>29</v>
       </c>
       <c r="D9" s="1">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/aReport_card/2025_2026/Second_term/JSS1/Second_term_JSS1_Civic_Education.xlsx
+++ b/aReport_card/2025_2026/Second_term/JSS1/Second_term_JSS1_Civic_Education.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22200323-76CA-449C-8006-DF9DB2F80A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBD2B07-552C-40D3-8EB2-141E673378D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="21">
   <si>
     <t>Admission_no</t>
   </si>
@@ -507,8 +507,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <f>C2+D2+E2</f>
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -519,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1">
         <v>36</v>
@@ -528,8 +527,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <f>C3+D3+E3</f>
-        <v>69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -549,8 +547,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <f>C4+D4+E4</f>
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -561,13 +558,13 @@
         <v>13</v>
       </c>
       <c r="C5" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -601,10 +598,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="1">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -621,7 +618,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1">
         <v>35</v>
